--- a/BTech/ID1104 Specifications.xlsx
+++ b/BTech/ID1104 Specifications.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BSDU\BTech\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BSDU_GIT\BTech\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -281,7 +281,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -512,7 +512,7 @@
     <col min="2" max="2" width="26.88671875" customWidth="1"/>
     <col min="3" max="3" width="32.88671875" customWidth="1"/>
     <col min="4" max="4" width="10.88671875" customWidth="1"/>
-    <col min="8" max="8" width="21.21875" customWidth="1"/>
+    <col min="8" max="8" width="26.109375" customWidth="1"/>
     <col min="9" max="9" width="31" customWidth="1"/>
     <col min="15" max="15" width="27.33203125" customWidth="1"/>
     <col min="16" max="16" width="37.109375" customWidth="1"/>
@@ -580,7 +580,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="409.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="361.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>1</v>
       </c>

--- a/BTech/ID1104 Specifications.xlsx
+++ b/BTech/ID1104 Specifications.xlsx
@@ -164,11 +164,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -640,7 +642,9 @@
       </c>
     </row>
     <row r="3" spans="1:19" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
